--- a/data/trans_orig/P23_1_2016_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>245824</t>
+          <t>245912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>284815</t>
+          <t>286396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251048</t>
+          <t>251173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286339</t>
+          <t>287162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507338</t>
+          <t>508749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>562938</t>
+          <t>564080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44797</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34215</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>113126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151689</t>
+          <t>152184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77931</t>
+          <t>77972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110773</t>
+          <t>110725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201444</t>
+          <t>198938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>254970</t>
+          <t>253233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>252602</t>
+          <t>251105</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>301282</t>
+          <t>300042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>267761</t>
+          <t>265960</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>310930</t>
+          <t>312631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>532089</t>
+          <t>534954</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>598671</t>
+          <t>600613</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>66651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>75882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94595</t>
+          <t>94188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135623</t>
+          <t>133767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>63127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>212805</t>
+          <t>211732</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>261565</t>
+          <t>258907</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168340</t>
+          <t>167690</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211125</t>
+          <t>212554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>391242</t>
+          <t>393145</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>456413</t>
+          <t>457434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289876</t>
+          <t>288958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341003</t>
+          <t>342064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>312772</t>
+          <t>316182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364363</t>
+          <t>366497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>620462</t>
+          <t>617319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>692525</t>
+          <t>691344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69404</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104930</t>
+          <t>105167</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81317</t>
+          <t>83822</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118800</t>
+          <t>119584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>159643</t>
+          <t>161599</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>214404</t>
+          <t>213216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31678</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44822</t>
+          <t>44238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222483</t>
+          <t>219718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273695</t>
+          <t>272188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187564</t>
+          <t>184908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>234913</t>
+          <t>233602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419753</t>
+          <t>419778</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>494175</t>
+          <t>488753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211363</t>
+          <t>213682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>261244</t>
+          <t>262412</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>288332</t>
+          <t>290819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341772</t>
+          <t>339346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>512781</t>
+          <t>516523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>586839</t>
+          <t>590369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111072</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155131</t>
+          <t>154402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82840</t>
+          <t>82721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122779</t>
+          <t>120379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>204517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261649</t>
+          <t>261660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36536</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244297</t>
+          <t>241423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296445</t>
+          <t>295637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>193504</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241546</t>
+          <t>239615</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>452296</t>
+          <t>448616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>526976</t>
+          <t>520140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148163</t>
+          <t>148631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192225</t>
+          <t>193751</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>287913</t>
+          <t>290860</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333333</t>
+          <t>335220</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>448167</t>
+          <t>451515</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>515010</t>
+          <t>516207</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139555</t>
+          <t>139370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181454</t>
+          <t>180395</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53319</t>
+          <t>53524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87112</t>
+          <t>87611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202559</t>
+          <t>199570</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259153</t>
+          <t>257241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26787</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>118099</t>
+          <t>117309</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>159792</t>
+          <t>159105</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>88031</t>
+          <t>89478</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>126966</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>216047</t>
+          <t>218898</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>275038</t>
+          <t>273471</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116547</t>
+          <t>117837</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153011</t>
+          <t>152263</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>298872</t>
+          <t>300848</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>328767</t>
+          <t>330712</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>422702</t>
+          <t>422968</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>474183</t>
+          <t>476280</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124558</t>
+          <t>123679</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>158895</t>
+          <t>159711</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>45285</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>151553</t>
+          <t>151316</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>197712</t>
+          <t>196677</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>37940</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65014</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39656</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>60881</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>93945</t>
+          <t>96774</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>95557</t>
+          <t>95902</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>123837</t>
+          <t>124055</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>376740</t>
+          <t>375845</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>392498</t>
+          <t>393109</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>474628</t>
+          <t>474401</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>517273</t>
+          <t>516957</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>108477</t>
+          <t>108564</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>136447</t>
+          <t>135746</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>108366</t>
+          <t>107236</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>145487</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>33602</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1451376</t>
+          <t>1449245</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1566437</t>
+          <t>1566820</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2165439</t>
+          <t>2176920</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2285150</t>
+          <t>2290098</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3656461</t>
+          <t>3658622</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3824575</t>
+          <t>3832103</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>657162</t>
+          <t>657993</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>752570</t>
+          <t>752729</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1034000</t>
+          <t>1025856</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1154938</t>
+          <t>1154919</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>107230</t>
+          <t>105115</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>92247</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>134015</t>
+          <t>137785</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>185244</t>
+          <t>188696</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1033109</t>
+          <t>1033431</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1146631</t>
+          <t>1147404</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>796934</t>
+          <t>795476</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>900794</t>
+          <t>897454</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1858282</t>
+          <t>1860794</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2016034</t>
+          <t>2010892</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2023</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>268364</t>
+          <t>266507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327404</t>
+          <t>326965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208694</t>
+          <t>210729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>249078</t>
+          <t>250871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>488953</t>
+          <t>488032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>563479</t>
+          <t>565454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43515</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>47312</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>53775</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48114</t>
+          <t>47588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100978</t>
+          <t>99669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37326</t>
+          <t>38648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71419</t>
+          <t>75137</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99032</t>
+          <t>93388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161063</t>
+          <t>157554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>229628</t>
+          <t>229494</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279789</t>
+          <t>281072</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>333122</t>
+          <t>334036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>418575</t>
+          <t>420416</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>575141</t>
+          <t>577395</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>693896</t>
+          <t>695282</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>33672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69300</t>
+          <t>70439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48317</t>
+          <t>51039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101662</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150041</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64154</t>
+          <t>63595</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131612</t>
+          <t>129226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>173471</t>
+          <t>176341</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>266453</t>
+          <t>266428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>319340</t>
+          <t>318700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365650</t>
+          <t>363894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335849</t>
+          <t>335992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371971</t>
+          <t>372130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667489</t>
+          <t>665942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723672</t>
+          <t>725112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60409</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>41421</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>63772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80141</t>
+          <t>80650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116961</t>
+          <t>119816</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119488</t>
+          <t>121307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160564</t>
+          <t>161167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108903</t>
+          <t>109642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141523</t>
+          <t>141854</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>238777</t>
+          <t>237454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>289536</t>
+          <t>289355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>150848</t>
+          <t>151817</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>497686</t>
+          <t>500106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>439201</t>
+          <t>438803</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>500786</t>
+          <t>505203</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>478763</t>
+          <t>492525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>979255</t>
+          <t>981529</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134779</t>
+          <t>134658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>661235</t>
+          <t>640394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71234</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102406</t>
+          <t>102912</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218083</t>
+          <t>215490</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>924638</t>
+          <t>894997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27722</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38231</t>
+          <t>38830</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>81209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256658</t>
+          <t>257852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118424</t>
+          <t>121178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161770</t>
+          <t>163058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>178274</t>
+          <t>189176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>388692</t>
+          <t>390456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208888</t>
+          <t>206189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250527</t>
+          <t>249846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>322879</t>
+          <t>322516</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>357232</t>
+          <t>356171</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>540108</t>
+          <t>539411</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>596790</t>
+          <t>598165</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7907,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140951</t>
+          <t>138495</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181706</t>
+          <t>180474</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75353</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>220336</t>
+          <t>220115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269672</t>
+          <t>269526</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>143138</t>
+          <t>145378</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>184749</t>
+          <t>188167</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>96126</t>
+          <t>95563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>123874</t>
+          <t>124615</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>252193</t>
+          <t>250685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>301682</t>
+          <t>300699</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>129413</t>
+          <t>129184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>158096</t>
+          <t>159002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>459264</t>
+          <t>458577</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>568421</t>
+          <t>567730</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>564097</t>
+          <t>566984</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>796284</t>
+          <t>814694</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141113</t>
+          <t>140288</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>170654</t>
+          <t>170158</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>75053</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>110951</t>
+          <t>102857</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261224</t>
+          <t>263555</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>55790</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>81009</t>
+          <t>79205</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69624</t>
+          <t>70335</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61240</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>144757</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>132480</t>
+          <t>133259</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>158910</t>
+          <t>160058</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>394399</t>
+          <t>394714</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>408457</t>
+          <t>408076</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>530738</t>
+          <t>531112</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>563493</t>
+          <t>565608</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -9045,12 +9045,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>104952</t>
+          <t>104129</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>130884</t>
+          <t>130017</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9060,12 +9060,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24263</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>121163</t>
+          <t>119826</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>153162</t>
+          <t>151806</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>301</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>516</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9243,12 +9243,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -9271,12 +9271,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26204</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9321,12 +9321,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32723</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1387859</t>
+          <t>1312916</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1932155</t>
+          <t>1930270</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2579319</t>
+          <t>2577228</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2873419</t>
+          <t>2847425</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3913971</t>
+          <t>3958696</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4690388</t>
+          <t>4683345</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -9614,12 +9614,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>637003</t>
+          <t>641386</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1404653</t>
+          <t>1477012</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>261388</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>377059</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>946969</t>
+          <t>950224</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1975074</t>
+          <t>1829952</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -9727,12 +9727,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>104919</t>
+          <t>103371</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>86583</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>112110</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>174954</t>
+          <t>177347</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9812,12 +9812,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -9840,12 +9840,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>613920</t>
+          <t>600359</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>844674</t>
+          <t>838145</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>463952</t>
+          <t>483868</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>640144</t>
+          <t>643754</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1168029</t>
+          <t>1165792</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1454703</t>
+          <t>1459122</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9925,12 +9925,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>245912</t>
+          <t>246722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>286396</t>
+          <t>285384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251173</t>
+          <t>250842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287162</t>
+          <t>286978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>508749</t>
+          <t>508955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>564080</t>
+          <t>564082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21552</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43394</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>33647</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113126</t>
+          <t>113723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152184</t>
+          <t>152709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77972</t>
+          <t>77635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110725</t>
+          <t>110556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198938</t>
+          <t>198787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>253233</t>
+          <t>250949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>251105</t>
+          <t>253959</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>300042</t>
+          <t>304049</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>265960</t>
+          <t>266602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>312631</t>
+          <t>313875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>534954</t>
+          <t>532292</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>600613</t>
+          <t>599624</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38301</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66651</t>
+          <t>68109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47850</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75882</t>
+          <t>76725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94188</t>
+          <t>94160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133767</t>
+          <t>135462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>34499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>36421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>36419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63127</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211732</t>
+          <t>211364</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>258907</t>
+          <t>260766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167690</t>
+          <t>166816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212554</t>
+          <t>211454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>393145</t>
+          <t>390176</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>457434</t>
+          <t>456144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288958</t>
+          <t>287869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342064</t>
+          <t>341097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316182</t>
+          <t>316649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366497</t>
+          <t>365596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>617319</t>
+          <t>618314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691344</t>
+          <t>695163</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>68503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105167</t>
+          <t>105646</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83822</t>
+          <t>80044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119584</t>
+          <t>116648</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>160561</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>213216</t>
+          <t>210585</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>31732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44238</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219718</t>
+          <t>222113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>272188</t>
+          <t>273597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184908</t>
+          <t>187652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>233602</t>
+          <t>233957</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419778</t>
+          <t>421579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>488753</t>
+          <t>492596</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213682</t>
+          <t>210951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>262412</t>
+          <t>264960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>290819</t>
+          <t>288710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>339346</t>
+          <t>340801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>516523</t>
+          <t>514212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>590369</t>
+          <t>586098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111307</t>
+          <t>111618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154402</t>
+          <t>152696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82721</t>
+          <t>83323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120379</t>
+          <t>120604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204517</t>
+          <t>206377</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261660</t>
+          <t>260147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18333</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24930</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37803</t>
+          <t>35506</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>241423</t>
+          <t>242752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>295637</t>
+          <t>295686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193504</t>
+          <t>189757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239615</t>
+          <t>239810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>448616</t>
+          <t>449322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520140</t>
+          <t>521932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148631</t>
+          <t>150711</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>193751</t>
+          <t>192054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>290860</t>
+          <t>289617</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>335220</t>
+          <t>334137</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>451515</t>
+          <t>450045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>516207</t>
+          <t>515493</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139370</t>
+          <t>139900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180395</t>
+          <t>184652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87611</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>199570</t>
+          <t>200352</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>257241</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117309</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>159105</t>
+          <t>157269</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89478</t>
+          <t>87931</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>126966</t>
+          <t>126182</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>218898</t>
+          <t>215626</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>273471</t>
+          <t>275310</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117837</t>
+          <t>114532</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152263</t>
+          <t>151408</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>300848</t>
+          <t>301278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>330712</t>
+          <t>331039</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>422968</t>
+          <t>421098</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>476280</t>
+          <t>473676</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>125024</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>159711</t>
+          <t>161659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>44016</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>151316</t>
+          <t>151478</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>196677</t>
+          <t>195831</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>64805</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>38505</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>62709</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>96774</t>
+          <t>98672</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>95902</t>
+          <t>96030</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>124055</t>
+          <t>123960</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>375845</t>
+          <t>376489</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>393109</t>
+          <t>393191</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>474401</t>
+          <t>473386</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>516957</t>
+          <t>516481</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>108564</t>
+          <t>107249</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>135746</t>
+          <t>135265</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>107236</t>
+          <t>108375</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>145487</t>
+          <t>148394</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1449245</t>
+          <t>1454347</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1566820</t>
+          <t>1567651</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2176920</t>
+          <t>2166418</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2290098</t>
+          <t>2286805</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3658622</t>
+          <t>3660422</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3832103</t>
+          <t>3829403</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>657993</t>
+          <t>652164</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>752729</t>
+          <t>749469</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1025856</t>
+          <t>1030338</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1154919</t>
+          <t>1155140</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>69222</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>105115</t>
+          <t>105992</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>93802</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>137785</t>
+          <t>134654</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>188696</t>
+          <t>186034</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1033431</t>
+          <t>1043197</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1147404</t>
+          <t>1147034</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>795476</t>
+          <t>796790</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>897454</t>
+          <t>904834</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1860794</t>
+          <t>1860282</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2010892</t>
+          <t>2013913</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -5513,32 +5513,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>300700</t>
+          <t>308175</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266507</t>
+          <t>277373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>326965</t>
+          <t>334000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5548,32 +5548,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>230666</t>
+          <t>271167</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210729</t>
+          <t>245442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250871</t>
+          <t>292282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5583,32 +5583,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>531366</t>
+          <t>579343</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>488032</t>
+          <t>543234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>565454</t>
+          <t>612848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -5626,32 +5626,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5661,32 +5661,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5696,32 +5696,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44159</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -5739,32 +5739,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>40634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5774,32 +5774,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5809,32 +5809,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -5852,32 +5852,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69802</t>
+          <t>72434</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47588</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99669</t>
+          <t>99817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5887,32 +5887,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53632</t>
+          <t>60458</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38648</t>
+          <t>42661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75137</t>
+          <t>83272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5922,32 +5922,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>123434</t>
+          <t>132892</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93388</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157554</t>
+          <t>162917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -5965,17 +5965,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6000,17 +6000,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6035,17 +6035,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6082,32 +6082,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>255862</t>
+          <t>289540</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>229494</t>
+          <t>259563</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>281072</t>
+          <t>313437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6117,32 +6117,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>366035</t>
+          <t>344976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>334036</t>
+          <t>323191</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>420416</t>
+          <t>366599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6152,32 +6152,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>621897</t>
+          <t>634516</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>577395</t>
+          <t>598225</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>695282</t>
+          <t>669721</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -6195,32 +6195,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>14864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33672</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6230,32 +6230,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45273</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6265,32 +6265,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70439</t>
+          <t>79809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -6308,32 +6308,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>41360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6343,32 +6343,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6378,32 +6378,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19828</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>54110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -6421,32 +6421,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>137867</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103506</t>
+          <t>115915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150677</t>
+          <t>164701</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6456,32 +6456,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>104151</t>
+          <t>108856</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>89316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129226</t>
+          <t>130375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6491,32 +6491,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>229760</t>
+          <t>246724</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176341</t>
+          <t>213454</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>266428</t>
+          <t>278768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -6534,17 +6534,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6569,17 +6569,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6604,17 +6604,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6651,32 +6651,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>341556</t>
+          <t>402028</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318700</t>
+          <t>375355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>363894</t>
+          <t>425856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6686,32 +6686,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>354411</t>
+          <t>419180</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335992</t>
+          <t>399611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>372130</t>
+          <t>438119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6721,32 +6721,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>695967</t>
+          <t>821208</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665942</t>
+          <t>789063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>725112</t>
+          <t>853499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -6764,32 +6764,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>36787</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>67508</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6799,32 +6799,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63772</t>
+          <t>70812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6834,32 +6834,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80650</t>
+          <t>87762</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119816</t>
+          <t>127295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -6877,32 +6877,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>21863</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>18358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30925</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -6990,32 +6990,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>140107</t>
+          <t>155226</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121307</t>
+          <t>133692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161167</t>
+          <t>180110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7025,32 +7025,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>124797</t>
+          <t>134973</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109642</t>
+          <t>117096</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141854</t>
+          <t>152536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>264904</t>
+          <t>290199</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237454</t>
+          <t>260748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>289355</t>
+          <t>320647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -7103,17 +7103,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7138,17 +7138,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7220,32 +7220,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>353809</t>
+          <t>389582</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>151817</t>
+          <t>363148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>500106</t>
+          <t>417088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>461693</t>
+          <t>468556</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>438803</t>
+          <t>447751</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>505203</t>
+          <t>487521</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>815502</t>
+          <t>858138</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>492525</t>
+          <t>822944</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>981529</t>
+          <t>893289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -7333,32 +7333,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>348216</t>
+          <t>114573</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134658</t>
+          <t>95987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>640394</t>
+          <t>138397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7368,32 +7368,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102912</t>
+          <t>106677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>435326</t>
+          <t>207054</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215490</t>
+          <t>182650</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>894997</t>
+          <t>231193</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -7446,32 +7446,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7481,32 +7481,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7516,32 +7516,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27409</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -7559,32 +7559,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>176513</t>
+          <t>185478</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81209</t>
+          <t>161622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257852</t>
+          <t>209485</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7594,32 +7594,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>143571</t>
+          <t>152802</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121178</t>
+          <t>137249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163058</t>
+          <t>171033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7629,32 +7629,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>320084</t>
+          <t>338280</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>189176</t>
+          <t>310332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390456</t>
+          <t>368016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -7672,17 +7672,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7707,17 +7707,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7742,17 +7742,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7789,32 +7789,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228369</t>
+          <t>253849</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>206189</t>
+          <t>230864</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249846</t>
+          <t>277959</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7824,32 +7824,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>340027</t>
+          <t>380193</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>322516</t>
+          <t>362238</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>356171</t>
+          <t>398588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7859,32 +7859,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>568396</t>
+          <t>634043</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>539411</t>
+          <t>603396</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>598165</t>
+          <t>667312</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -7902,32 +7902,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>157857</t>
+          <t>166184</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138495</t>
+          <t>144550</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180474</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7937,32 +7937,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73334</t>
+          <t>81780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>108073</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7972,32 +7972,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>244056</t>
+          <t>260510</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>220115</t>
+          <t>234094</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269526</t>
+          <t>286549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -8015,32 +8015,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8050,32 +8050,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8085,32 +8085,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -8128,32 +8128,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>164767</t>
+          <t>178180</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>145378</t>
+          <t>157453</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>188167</t>
+          <t>200836</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8163,32 +8163,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>109552</t>
+          <t>120753</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>95563</t>
+          <t>107025</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>124615</t>
+          <t>136385</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8198,32 +8198,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>274319</t>
+          <t>298933</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>250685</t>
+          <t>273686</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>300699</t>
+          <t>327630</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -8241,17 +8241,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8311,17 +8311,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8358,32 +8358,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>144223</t>
+          <t>160595</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>129184</t>
+          <t>144253</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>159002</t>
+          <t>176681</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8393,32 +8393,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>513574</t>
+          <t>335352</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>458577</t>
+          <t>321061</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>567730</t>
+          <t>347783</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8428,32 +8428,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>657797</t>
+          <t>495947</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>566984</t>
+          <t>471500</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>814694</t>
+          <t>517801</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -8471,32 +8471,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>140288</t>
+          <t>154307</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>170158</t>
+          <t>187794</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8506,32 +8506,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46015</t>
+          <t>49251</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>40237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75053</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8541,32 +8541,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>201513</t>
+          <t>220853</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>102857</t>
+          <t>200765</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>263555</t>
+          <t>242314</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8619,32 +8619,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8654,32 +8654,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -8697,32 +8697,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>66954</t>
+          <t>73292</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55790</t>
+          <t>60810</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79205</t>
+          <t>88411</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8732,32 +8732,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>42970</t>
+          <t>47296</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>70335</t>
+          <t>58895</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8767,32 +8767,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>109923</t>
+          <t>120588</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>106207</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>144757</t>
+          <t>137692</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8880,17 +8880,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8927,32 +8927,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>146153</t>
+          <t>160436</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>133259</t>
+          <t>144483</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>160058</t>
+          <t>174188</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8962,32 +8962,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>401862</t>
+          <t>438196</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>394714</t>
+          <t>430607</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>408076</t>
+          <t>445343</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8997,32 +8997,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>548016</t>
+          <t>598632</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>531112</t>
+          <t>581656</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>565608</t>
+          <t>618622</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -9040,32 +9040,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>117575</t>
+          <t>129568</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>104129</t>
+          <t>116771</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>130017</t>
+          <t>145898</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9075,32 +9075,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9110,32 +9110,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>135250</t>
+          <t>149203</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>119826</t>
+          <t>131591</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>151806</t>
+          <t>166394</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9188,32 +9188,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>285</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9223,32 +9223,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -9266,32 +9266,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>13289</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9301,17 +9301,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9336,32 +9336,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>23310</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32737</t>
+          <t>34381</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -9379,17 +9379,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9414,17 +9414,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9449,17 +9449,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9496,32 +9496,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1770672</t>
+          <t>1964205</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1312916</t>
+          <t>1900089</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1930270</t>
+          <t>2028033</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9531,32 +9531,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2668268</t>
+          <t>2657623</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2577228</t>
+          <t>2611447</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2847425</t>
+          <t>2708244</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9566,32 +9566,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>4438940</t>
+          <t>4621828</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3958696</t>
+          <t>4541527</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4683345</t>
+          <t>4710838</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -9609,32 +9609,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>852438</t>
+          <t>663408</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>641386</t>
+          <t>618433</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1477012</t>
+          <t>708368</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9644,32 +9644,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>338037</t>
+          <t>366543</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>337336</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>377059</t>
+          <t>398317</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9679,32 +9679,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1190474</t>
+          <t>1029951</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>950224</t>
+          <t>976529</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1829952</t>
+          <t>1084078</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -9722,32 +9722,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>50492</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>103371</t>
+          <t>103793</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9757,32 +9757,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>86365</t>
+          <t>96077</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9792,32 +9792,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>140722</t>
+          <t>156421</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>112110</t>
+          <t>130668</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>177347</t>
+          <t>187011</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -9835,32 +9835,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>762156</t>
+          <t>822060</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>600359</t>
+          <t>768890</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>838145</t>
+          <t>882148</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9870,32 +9870,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>583579</t>
+          <t>630481</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>483868</t>
+          <t>590213</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>643754</t>
+          <t>675429</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9905,32 +9905,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1345734</t>
+          <t>1452540</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1165792</t>
+          <t>1381395</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1459122</t>
+          <t>1529462</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -9948,17 +9948,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -9983,17 +9983,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10018,17 +10018,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
